--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_ADR.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_ADR.xlsx
@@ -1,44 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Índice de decisiones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs y " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_3" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _3" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_4" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _5" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_6" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _6" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_7" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _7" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_8" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _8" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_9" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs _9" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_10" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs_10" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_11" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs_11" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_12" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs_12" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_13" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs_13" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_14" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs_14" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Alternativas Evaluadas_15" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Consecuencias, Trade-offs_15" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de trazabilidad (ADR → n" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Índice de decisiones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. Alternativas Evaluadas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="5. Consecuencias, Trade-offs y " sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2. Alternativas Evaluadas_2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. Consecuencias, Trade-offs _2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2. Alternativas Evaluadas_3" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5. Consecuencias, Trade-offs _3" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2. Alternativas Evaluadas_4" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5. Consecuencias, Trade-offs _4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2. Alternativas Evaluadas_5" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="5. Consecuencias, Trade-offs _5" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2. Alternativas Evaluadas_6" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="5. Consecuencias, Trade-offs _6" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2. Alternativas Evaluadas_7" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="5. Consecuencias, Trade-offs _7" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2. Alternativas Evaluadas_8" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="5. Consecuencias, Trade-offs _8" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2. Alternativas Evaluadas_9" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="5. Consecuencias, Trade-offs _9" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2. Alternativas Evaluadas_10" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="5. Consecuencias, Trade-offs_10" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2. Alternativas Evaluadas_11" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="5. Consecuencias, Trade-offs_11" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2. Alternativas Evaluadas_12" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="5. Consecuencias, Trade-offs_12" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2. Alternativas Evaluadas_13" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="5. Consecuencias, Trade-offs_13" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2. Alternativas Evaluadas_14" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="5. Consecuencias, Trade-offs_14" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2. Alternativas Evaluadas_15" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="5. Consecuencias, Trade-offs_15" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Matriz de trazabilidad (ADR → n" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Estilo arquitectónico: monolito modular (Django 5.x LTS / Python 3.12)</t>
+          <t>Estilo arquitectónico: monolito modular (Laravel 13 / PHP 8.5; Django queda como alternativa descartada) — propuesta</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>A. Keycloak IdP maestro en nube (ECS Fargate) + caché local de solo lectura TTL 8 h + offline tokens (8 h/14 h)</t>
+          <t>A. Keycloak IdP maestro en nube (ECS Fargate) + caché local de solo lectura de 24 h con verificador local de relevo + credencial de turno (8 h bodega / 14 h reparto)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>A. Monolito modular (Django 5.x LTS, Python 3.12)</t>
+          <t>A. Monolito modular (Django 5.x LTS, Python 3.12) — Alternativa sustituida el 25-09-2026 por el backend Laravel 13 / PHP 8.5; texto vigente en 14_m_decisiones_adr.tex.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>A. Cómputo elástico serverless/contenedores (Fargate 2→6, Celery 2→4, Lambda, Aurora escalada)</t>
+          <t>A. Cómputo elástico serverless/contenedores (Fargate 2→6, Celery 2→4, Lambda, Aurora escalada) — Alternativa sustituida el 25-09-2026 por el backend Laravel 13 / PHP 8.5; texto vigente en 14_m_decisiones_adr.tex.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Architecture Fitness Functions (ArchUnit/Django: contratos de módulo) en CI; revisión por módulo (RT-02.01)</t>
+          <t>Fitness functions de arquitectura en CI (reglas de dependencia entre los espacios de nombres PSR-4 de M1–M12); revisión por módulo (RT-02.01)</t>
         </is>
       </c>
     </row>
